--- a/output/pdf_financials_xlsx/PBH.xlsx
+++ b/output/pdf_financials_xlsx/PBH.xlsx
@@ -2255,16 +2255,16 @@
         <v>2.509</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>131.637</v>
+        <v>2.757</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>174.301</v>
+        <v>3.573</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>200.599</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>213.054</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
@@ -2324,16 +2324,16 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>149.305</v>
+        <v>20.425</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>193.488</v>
+        <v>22.76</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>223.071</v>
+        <v>22.472</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>229.604</v>
+        <v>16.55</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>14.171</v>
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>27.89480665791052</v>
+        <v>3.816023749960298</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>24.52530763107594</v>
+        <v>2.884912768147318</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>23.23344050643195</v>
+        <v>2.340518826116074</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>21.40356862865735</v>
+        <v>1.542782620530475</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>1.159848027251641</v>
@@ -6394,57 +6394,55 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.234</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.653</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.442</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.442</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.929</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>11.804</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>37.6</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>27.7</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>46.6</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="93">
@@ -12106,7 +12104,11 @@
           <t>Reserves (note 15)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -14300,7 +14302,11 @@
           <t>Reserves (note 14)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -15634,7 +15640,11 @@
           <t>Reserves (note 16)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -17816,7 +17826,11 @@
           <t>Reserves (note 17)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -18722,7 +18736,11 @@
           <t>Reserves (note 19)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -21904,7 +21922,11 @@
           <t>Reserves (note 20) 4,929</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -23254,7 +23276,11 @@
           <t>Reserves (note 20)</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -88666,7 +88692,7 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -90102,7 +90128,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -90210,7 +90236,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -93040,7 +93066,7 @@
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">

--- a/output/pdf_financials_xlsx/PBH.xlsx
+++ b/output/pdf_financials_xlsx/PBH.xlsx
@@ -2255,16 +2255,16 @@
         <v>2.509</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2.757</v>
+        <v>131.637</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>3.573</v>
+        <v>174.301</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>200.599</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>213.054</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
@@ -2324,16 +2324,16 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>20.425</v>
+        <v>149.305</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>22.76</v>
+        <v>193.488</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>22.472</v>
+        <v>223.071</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>16.55</v>
+        <v>229.604</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>14.171</v>
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3.816023749960298</v>
+        <v>27.89480665791052</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2.884912768147318</v>
+        <v>24.52530763107594</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2.340518826116074</v>
+        <v>23.23344050643195</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.542782620530475</v>
+        <v>21.40356862865735</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>1.159848027251641</v>
@@ -88692,7 +88692,7 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -90128,7 +90128,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -90236,7 +90236,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -93066,7 +93066,7 @@
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">

--- a/output/pdf_financials_xlsx/PBH.xlsx
+++ b/output/pdf_financials_xlsx/PBH.xlsx
@@ -2255,19 +2255,19 @@
         <v>2.509</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>131.637</v>
+        <v>2.757</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>174.301</v>
+        <v>3.573</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>200.599</v>
+        <v>4.836</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>213.054</v>
+        <v>4.371</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>4.356</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.5</v>
@@ -2324,19 +2324,19 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>149.305</v>
+        <v>20.425</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>193.488</v>
+        <v>22.76</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>223.071</v>
+        <v>27.308</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>229.604</v>
+        <v>20.921</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>14.171</v>
+        <v>18.527</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>59.1</v>
@@ -2393,19 +2393,19 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>27.89480665791052</v>
+        <v>3.816023749960298</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>24.52530763107594</v>
+        <v>2.884912768147318</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>23.23344050643195</v>
+        <v>2.844201143804634</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>21.40356862865735</v>
+        <v>1.950245027439158</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.159848027251641</v>
+        <v>1.516371773402805</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>3.981138430447962</v>
@@ -6875,16 +6875,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>2.509</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>2.757</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>3.573</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -6896,31 +6896,31 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>20.6</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -35800,7 +35800,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E262" s="5" t="n">
@@ -73594,7 +73594,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -77900,7 +77900,7 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -81250,7 +81250,7 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
@@ -85934,7 +85934,7 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -90552,7 +90552,7 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
